--- a/business_forms/046_property_energy_efficiency_program_application_form--business_forms.xlsx
+++ b/business_forms/046_property_energy_efficiency_program_application_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1029,12 +1029,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C56"/>
+  <dimension ref="A1:C54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1062,12 +1062,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'al'}</t>
+          <t>al</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'AL'}</t>
+          <t>AL</t>
         </is>
       </c>
     </row>
@@ -1079,12 +1079,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'ak'}</t>
+          <t>ak</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'AK'}</t>
+          <t>AK</t>
         </is>
       </c>
     </row>
@@ -1096,12 +1096,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'az'}</t>
+          <t>az</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'AZ'}</t>
+          <t>AZ</t>
         </is>
       </c>
     </row>
@@ -1113,12 +1113,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'ca'}</t>
+          <t>ca</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'CA'}</t>
+          <t>CA</t>
         </is>
       </c>
     </row>
@@ -1130,12 +1130,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'co'}</t>
+          <t>co</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'CO'}</t>
+          <t>CO</t>
         </is>
       </c>
     </row>
@@ -1147,12 +1147,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'ct'}</t>
+          <t>ct</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'CT'}</t>
+          <t>CT</t>
         </is>
       </c>
     </row>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_'fl'}</t>
+          <t>fl</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 'FL'}</t>
+          <t>FL</t>
         </is>
       </c>
     </row>
@@ -1181,12 +1181,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_8,_'name':_'hi'}</t>
+          <t>hi</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 8, 'name': 'HI'}</t>
+          <t>HI</t>
         </is>
       </c>
     </row>
@@ -1198,12 +1198,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_9,_'name':_'id'}</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 9, 'name': 'ID'}</t>
+          <t>ID</t>
         </is>
       </c>
     </row>
@@ -1215,12 +1215,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_10,_'name':_'il'}</t>
+          <t>il</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 10, 'name': 'IL'}</t>
+          <t>IL</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_11,_'name':_'in'}</t>
+          <t>in</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 11, 'name': 'IN'}</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
@@ -1249,12 +1249,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_12,_'name':_'ia'}</t>
+          <t>ia</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 12, 'name': 'IA'}</t>
+          <t>IA</t>
         </is>
       </c>
     </row>
@@ -1266,12 +1266,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_13,_'name':_'ks'}</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 13, 'name': 'KS'}</t>
+          <t>KS</t>
         </is>
       </c>
     </row>
@@ -1283,12 +1283,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_14,_'name':_'ky'}</t>
+          <t>ky</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 14, 'name': 'KY'}</t>
+          <t>KY</t>
         </is>
       </c>
     </row>
@@ -1300,12 +1300,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_15,_'name':_'la'}</t>
+          <t>la</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 15, 'name': 'LA'}</t>
+          <t>LA</t>
         </is>
       </c>
     </row>
@@ -1317,12 +1317,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_16,_'name':_'ma'}</t>
+          <t>ma</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 16, 'name': 'MA'}</t>
+          <t>MA</t>
         </is>
       </c>
     </row>
@@ -1334,12 +1334,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_17,_'name':_'md'}</t>
+          <t>md</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 17, 'name': 'MD'}</t>
+          <t>MD</t>
         </is>
       </c>
     </row>
@@ -1351,12 +1351,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_18,_'name':_'ma'}</t>
+          <t>me</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 18, 'name': 'MA'}</t>
+          <t>ME</t>
         </is>
       </c>
     </row>
@@ -1368,12 +1368,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_19,_'name':_'me'}</t>
+          <t>mi</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 19, 'name': 'ME'}</t>
+          <t>MI</t>
         </is>
       </c>
     </row>
@@ -1385,12 +1385,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_20,_'name':_'mi'}</t>
+          <t>mn</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 20, 'name': 'MI'}</t>
+          <t>MN</t>
         </is>
       </c>
     </row>
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_21,_'name':_'mn'}</t>
+          <t>mo</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 21, 'name': 'MN'}</t>
+          <t>MO</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_22,_'name':_'mo'}</t>
+          <t>ms</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 22, 'name': 'MO'}</t>
+          <t>MS</t>
         </is>
       </c>
     </row>
@@ -1436,12 +1436,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_23,_'name':_'ms'}</t>
+          <t>mt</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 23, 'name': 'MS'}</t>
+          <t>MT</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_24,_'name':_'mt'}</t>
+          <t>nc</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 24, 'name': 'MT'}</t>
+          <t>NC</t>
         </is>
       </c>
     </row>
@@ -1470,12 +1470,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_25,_'name':_'nc'}</t>
+          <t>nd</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 25, 'name': 'NC'}</t>
+          <t>ND</t>
         </is>
       </c>
     </row>
@@ -1487,12 +1487,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_26,_'name':_'nd'}</t>
+          <t>ne</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 26, 'name': 'ND'}</t>
+          <t>NE</t>
         </is>
       </c>
     </row>
@@ -1504,12 +1504,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_27,_'name':_'ne'}</t>
+          <t>nh</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 27, 'name': 'NE'}</t>
+          <t>NH</t>
         </is>
       </c>
     </row>
@@ -1521,12 +1521,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_28,_'name':_'nh'}</t>
+          <t>nj</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 28, 'name': 'NH'}</t>
+          <t>NJ</t>
         </is>
       </c>
     </row>
@@ -1538,12 +1538,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_29,_'name':_'nj'}</t>
+          <t>nm</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 29, 'name': 'NJ'}</t>
+          <t>NM</t>
         </is>
       </c>
     </row>
@@ -1555,12 +1555,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_30,_'name':_'nm'}</t>
+          <t>nv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 30, 'name': 'NM'}</t>
+          <t>NV</t>
         </is>
       </c>
     </row>
@@ -1572,12 +1572,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_31,_'name':_'nv'}</t>
+          <t>ny</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 31, 'name': 'NV'}</t>
+          <t>NY</t>
         </is>
       </c>
     </row>
@@ -1589,12 +1589,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_32,_'name':_'ny'}</t>
+          <t>oh</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 32, 'name': 'NY'}</t>
+          <t>OH</t>
         </is>
       </c>
     </row>
@@ -1606,12 +1606,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_33,_'name':_'oh'}</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 33, 'name': 'OH'}</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -1623,12 +1623,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_34,_'name':_'ok'}</t>
+          <t>or</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 34, 'name': 'OK'}</t>
+          <t>OR</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_35,_'name':_'or'}</t>
+          <t>pa</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 35, 'name': 'OR'}</t>
+          <t>PA</t>
         </is>
       </c>
     </row>
@@ -1657,12 +1657,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_36,_'name':_'pa'}</t>
+          <t>ri</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 36, 'name': 'PA'}</t>
+          <t>RI</t>
         </is>
       </c>
     </row>
@@ -1674,12 +1674,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_37,_'name':_'ri'}</t>
+          <t>sc</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': 37, 'name': 'RI'}</t>
+          <t>SC</t>
         </is>
       </c>
     </row>
@@ -1691,12 +1691,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'id':_38,_'name':_'sc'}</t>
+          <t>sd</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'id': 38, 'name': 'SC'}</t>
+          <t>SD</t>
         </is>
       </c>
     </row>
@@ -1708,12 +1708,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'id':_39,_'name':_'sd'}</t>
+          <t>tn</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'id': 39, 'name': 'SD'}</t>
+          <t>TN</t>
         </is>
       </c>
     </row>
@@ -1725,12 +1725,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'id':_40,_'name':_'tn'}</t>
+          <t>tx</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'id': 40, 'name': 'TN'}</t>
+          <t>TX</t>
         </is>
       </c>
     </row>
@@ -1742,12 +1742,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'id':_41,_'name':_'tx'}</t>
+          <t>ut</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'id': 41, 'name': 'TX'}</t>
+          <t>UT</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'id':_42,_'name':_'ut'}</t>
+          <t>va</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'id': 42, 'name': 'UT'}</t>
+          <t>VA</t>
         </is>
       </c>
     </row>
@@ -1776,12 +1776,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'id':_43,_'name':_'va'}</t>
+          <t>vt</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'id': 43, 'name': 'VA'}</t>
+          <t>VT</t>
         </is>
       </c>
     </row>
@@ -1793,12 +1793,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'id':_44,_'name':_'vt'}</t>
+          <t>wa</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'id': 44, 'name': 'VT'}</t>
+          <t>WA</t>
         </is>
       </c>
     </row>
@@ -1810,12 +1810,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'id':_45,_'name':_'wa'}</t>
+          <t>wv</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'id': 45, 'name': 'WA'}</t>
+          <t>WV</t>
         </is>
       </c>
     </row>
@@ -1827,12 +1827,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'id':_46,_'name':_'wv'}</t>
+          <t>wi</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'id': 46, 'name': 'WV'}</t>
+          <t>WI</t>
         </is>
       </c>
     </row>
@@ -1844,46 +1844,46 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'id':_47,_'name':_'wi'}</t>
+          <t>wy</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'id': 47, 'name': 'WI'}</t>
+          <t>WY</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>state_choices</t>
+          <t>upgrade_type_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'id':_48,_'name':_'wv'}</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'id': 48, 'name': 'WV'}</t>
+          <t>Solar</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>state_choices</t>
+          <t>upgrade_type_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'id':_49,_'name':_'wy'}</t>
+          <t>led_lighting</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'id': 49, 'name': 'WY'}</t>
+          <t>LED Lighting</t>
         </is>
       </c>
     </row>
@@ -1895,12 +1895,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'id':_51,_'name':_'solar'}</t>
+          <t>hvac</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'id': 51, 'name': 'Solar'}</t>
+          <t>HVAC</t>
         </is>
       </c>
     </row>
@@ -1912,12 +1912,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'id':_52,_'name':_'led_lighting'}</t>
+          <t>windows</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'id': 52, 'name': 'LED Lighting'}</t>
+          <t>Windows</t>
         </is>
       </c>
     </row>
@@ -1929,12 +1929,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'id':_53,_'name':_'hvac'}</t>
+          <t>doors</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'id': 53, 'name': 'HVAC'}</t>
+          <t>Doors</t>
         </is>
       </c>
     </row>
@@ -1946,46 +1946,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'id':_54,_'name':_'windows'}</t>
+          <t>roofing</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'id': 54, 'name': 'Windows'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>upgrade_type_choices</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>{'id':_55,_'name':_'doors'}</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>{'id': 55, 'name': 'Doors'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>upgrade_type_choices</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>{'id':_56,_'name':_'roofing'}</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>{'id': 56, 'name': 'Roofing'}</t>
+          <t>Roofing</t>
         </is>
       </c>
     </row>
